--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -564,7 +564,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>14</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -733,13 +733,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -896,10 +896,10 @@
         <v>14</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
         <v>6</v>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -88,10 +88,10 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>COBOS</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -103,25 +103,28 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VEGA</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>SOTO</t>
@@ -130,22 +133,28 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>YOLET</t>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>IGNACIO</t>
@@ -157,16 +166,19 @@
     <t>JOSE</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
   </si>
 </sst>
 </file>
@@ -736,16 +748,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -759,16 +774,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -782,16 +800,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -805,16 +826,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -828,16 +852,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>88.45999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -893,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>64.09999999999999</v>
+        <v>61.54</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -919,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>79.17</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -971,16 +998,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -997,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>80.77</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,10 +1081,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,22 +1098,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920318</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1094,16 +1121,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920007</v>
+        <v>22330051920378</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1123,10 +1150,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1149,7 +1176,7 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1169,10 +1196,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1186,62 +1213,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920390</v>
+        <v>22330051920394</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920046</v>
+        <v>22330051920222</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920057</v>
+        <v>21330051920390</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1250,29 +1277,52 @@
         <v>15</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920067</v>
+        <v>22330051920359</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920363</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -146,9 +140,6 @@
   </si>
   <si>
     <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
   </si>
   <si>
     <t>ARACELY</t>
@@ -1043,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,22 +1066,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920247</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1098,16 +1089,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>22330051920378</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1121,22 +1112,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920378</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1144,16 +1135,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1167,16 +1158,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920405</v>
+        <v>22330051920273</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1190,22 +1181,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920273</v>
+        <v>22330051920394</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1213,16 +1204,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920394</v>
+        <v>22330051920222</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1236,22 +1227,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920222</v>
+        <v>21330051920390</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1259,39 +1250,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920390</v>
+        <v>22330051920359</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920359</v>
+        <v>22330051920363</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1300,29 +1291,6 @@
         <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920363</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -85,91 +85,88 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>ARACELY</t>
   </si>
   <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>IGNACIO</t>
+    <t>OSMAR</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
 </sst>
 </file>
@@ -911,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>61.54</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -946,7 +943,7 @@
         <v>79.17</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -972,7 +969,7 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -998,7 +995,7 @@
         <v>84</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1015,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>88.45999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1066,22 +1063,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920190</v>
+        <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1089,16 +1086,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920378</v>
+        <v>22330051920389</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1107,58 +1104,58 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920405</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920273</v>
+        <v>22330051920378</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1167,21 +1164,21 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920394</v>
+        <v>22330051920363</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1190,82 +1187,82 @@
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920222</v>
+        <v>22330051920405</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920390</v>
+        <v>21330051920002</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920359</v>
+        <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1273,22 +1270,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920363</v>
+        <v>21330051920059</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>1</v>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -88,12 +88,12 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>SOTO</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>LAGUNA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
@@ -908,16 +911,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>79.48999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1086,7 +1089,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920389</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1101,15 +1104,15 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920389</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1132,13 +1135,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920190</v>
+        <v>22330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>43</v>
@@ -1155,13 +1158,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920378</v>
+        <v>22330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -1178,13 +1181,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920363</v>
+        <v>22330051920378</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
@@ -1201,13 +1204,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>22330051920363</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>46</v>
@@ -1216,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1224,13 +1227,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920002</v>
+        <v>22330051920405</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -1239,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1247,13 +1250,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920374</v>
+        <v>21330051920002</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
@@ -1270,24 +1273,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920059</v>
+        <v>22330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>49</v>
       </c>
       <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920059</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>15</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -85,24 +85,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
     <t>ANGELES</t>
   </si>
   <si>
@@ -112,24 +115,27 @@
     <t>ROMANOS</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
@@ -139,25 +145,28 @@
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
@@ -911,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -1034,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,16 +1075,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1095,10 +1104,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1118,10 +1127,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1141,10 +1150,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1164,10 +1173,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1187,10 +1196,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1210,10 +1219,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1227,16 +1236,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>21330051920396</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1250,22 +1259,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920002</v>
+        <v>22330051920405</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1273,16 +1282,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920374</v>
+        <v>21330051920002</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1296,24 +1305,47 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920059</v>
+        <v>22330051920374</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920059</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
         <v>10</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -929,7 +929,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -955,7 +955,7 @@
         <v>79.17</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -981,7 +981,7 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1007,7 +1007,7 @@
         <v>84</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1033,7 +1033,7 @@
         <v>92.31</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -112,9 +112,6 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
     <t>JORGE</t>
   </si>
   <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
@@ -176,9 +170,6 @@
   </si>
   <si>
     <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
 </sst>
 </file>
@@ -929,7 +920,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -955,7 +946,7 @@
         <v>79.17</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -981,7 +972,7 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1007,7 +998,7 @@
         <v>84</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1024,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>92.31</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1081,10 +1072,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1104,10 +1095,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1127,10 +1118,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1150,10 +1141,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1173,10 +1164,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1196,10 +1187,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1219,10 +1210,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1242,10 +1233,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1268,7 +1259,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1288,10 +1279,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1311,10 +1302,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1323,29 +1314,6 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920059</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>
